--- a/out/27S/ver2/27S_ver2_instructor.xlsx
+++ b/out/27S/ver2/27S_ver2_instructor.xlsx
@@ -103,12 +103,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00E6F3FF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00E6FFE6"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF2E6"/>
+        <fgColor rgb="00FFE6F2"/>
       </patternFill>
     </fill>
     <fill>
@@ -118,17 +123,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E6F3FF"/>
+        <fgColor rgb="00F0E6FF"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFE6F2"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F0E6FF"/>
+        <fgColor rgb="00FFF2E6"/>
       </patternFill>
     </fill>
   </fills>
@@ -206,12 +206,12 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="8" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -814,11 +814,29 @@
           <t>2:00 PM</t>
         </is>
       </c>
-      <c r="B15" s="4" t="n"/>
+      <c r="B15" s="9" t="inlineStr">
+        <is>
+          <t>STAT 2163-004
+Corley 104
+2:00 PM-2:50 PM</t>
+        </is>
+      </c>
       <c r="C15" s="6" t="n"/>
-      <c r="D15" s="4" t="n"/>
+      <c r="D15" s="9" t="inlineStr">
+        <is>
+          <t>STAT 2163-004
+Corley 104
+2:00 PM-2:50 PM</t>
+        </is>
+      </c>
       <c r="E15" s="6" t="n"/>
-      <c r="F15" s="4" t="n"/>
+      <c r="F15" s="9" t="inlineStr">
+        <is>
+          <t>STAT 2163-004
+Corley 104
+2:00 PM-2:50 PM</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="18" customHeight="1">
       <c r="A16" s="3" t="inlineStr">
@@ -826,11 +844,11 @@
           <t>2:30 PM</t>
         </is>
       </c>
-      <c r="B16" s="4" t="n"/>
+      <c r="B16" s="6" t="n"/>
       <c r="C16" s="4" t="n"/>
-      <c r="D16" s="4" t="n"/>
+      <c r="D16" s="6" t="n"/>
       <c r="E16" s="4" t="n"/>
-      <c r="F16" s="4" t="n"/>
+      <c r="F16" s="6" t="n"/>
     </row>
     <row r="17" ht="18" customHeight="1">
       <c r="A17" s="3" t="inlineStr">
@@ -881,26 +899,29 @@
       <c r="F20" s="4" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="9" t="inlineStr">
+      <c r="A23" s="10" t="inlineStr">
         <is>
           <t>Online / TBA</t>
         </is>
       </c>
-      <c r="B23" s="10" t="inlineStr">
-        <is>
-          <t>MATH 1203-TC1, STAT 2163-TC1, STAT 2163-TC2</t>
+      <c r="B23" s="11" t="inlineStr">
+        <is>
+          <t>STAT 2163-TC1, STAT 2163-TC2</t>
         </is>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A2:F20"/>
-  <mergeCells count="7">
+  <mergeCells count="10">
     <mergeCell ref="E13:E15"/>
     <mergeCell ref="C13:C15"/>
+    <mergeCell ref="D15:D16"/>
+    <mergeCell ref="F15:F16"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="B23:F23"/>
     <mergeCell ref="F5:F6"/>
     <mergeCell ref="B5:B6"/>
+    <mergeCell ref="B15:B16"/>
     <mergeCell ref="D5:D6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1007,13 +1028,7 @@
         </is>
       </c>
       <c r="B6" s="4" t="n"/>
-      <c r="C6" s="11" t="inlineStr">
-        <is>
-          <t>MATH 2934-001
-Rothwell 207
-9:30 AM-10:50 AM</t>
-        </is>
-      </c>
+      <c r="C6" s="4" t="n"/>
       <c r="D6" s="4" t="n"/>
       <c r="E6" s="4" t="n"/>
       <c r="F6" s="4" t="n"/>
@@ -1024,29 +1039,11 @@
           <t>10:00 AM</t>
         </is>
       </c>
-      <c r="B7" s="11" t="inlineStr">
-        <is>
-          <t>MATH 2934-001
-Rothwell 207
-10:00 AM-10:50 AM</t>
-        </is>
-      </c>
-      <c r="C7" s="8" t="n"/>
-      <c r="D7" s="11" t="inlineStr">
-        <is>
-          <t>MATH 2934-001
-Rothwell 207
-10:00 AM-10:50 AM</t>
-        </is>
-      </c>
+      <c r="B7" s="4" t="n"/>
+      <c r="C7" s="4" t="n"/>
+      <c r="D7" s="4" t="n"/>
       <c r="E7" s="4" t="n"/>
-      <c r="F7" s="11" t="inlineStr">
-        <is>
-          <t>MATH 2934-001
-Rothwell 207
-10:00 AM-10:50 AM</t>
-        </is>
-      </c>
+      <c r="F7" s="4" t="n"/>
     </row>
     <row r="8" ht="18" customHeight="1">
       <c r="A8" s="3" t="inlineStr">
@@ -1054,11 +1051,11 @@
           <t>10:30 AM</t>
         </is>
       </c>
-      <c r="B8" s="6" t="n"/>
-      <c r="C8" s="6" t="n"/>
-      <c r="D8" s="6" t="n"/>
+      <c r="B8" s="4" t="n"/>
+      <c r="C8" s="4" t="n"/>
+      <c r="D8" s="4" t="n"/>
       <c r="E8" s="4" t="n"/>
-      <c r="F8" s="6" t="n"/>
+      <c r="F8" s="4" t="n"/>
     </row>
     <row r="9" ht="18" customHeight="1">
       <c r="A9" s="3" t="inlineStr">
@@ -1068,30 +1065,36 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>MATH 2934-002
-Corley 101
+          <t>MATH 1113-001
+Corley 104
 11:00 AM-11:50 AM</t>
         </is>
       </c>
-      <c r="C9" s="4" t="n"/>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>MATH 0903-001
+Corley 104
+11:00 AM-12:20 PM</t>
+        </is>
+      </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>MATH 2934-002
-Corley 101
+          <t>MATH 1113-001
+Corley 104
 11:00 AM-11:50 AM</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>MATH 2934-002
-Corley 101
+          <t>MATH 0903-001
+Corley 104
 11:00 AM-12:20 PM</t>
         </is>
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>MATH 2934-002
-Corley 101
+          <t>MATH 1113-001
+Corley 104
 11:00 AM-11:50 AM</t>
         </is>
       </c>
@@ -1103,7 +1106,7 @@
         </is>
       </c>
       <c r="B10" s="6" t="n"/>
-      <c r="C10" s="4" t="n"/>
+      <c r="C10" s="8" t="n"/>
       <c r="D10" s="6" t="n"/>
       <c r="E10" s="8" t="n"/>
       <c r="F10" s="6" t="n"/>
@@ -1115,7 +1118,7 @@
         </is>
       </c>
       <c r="B11" s="4" t="n"/>
-      <c r="C11" s="4" t="n"/>
+      <c r="C11" s="6" t="n"/>
       <c r="D11" s="4" t="n"/>
       <c r="E11" s="6" t="n"/>
       <c r="F11" s="4" t="n"/>
@@ -1229,12 +1232,12 @@
       <c r="F20" s="4" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="9" t="inlineStr">
+      <c r="A23" s="10" t="inlineStr">
         <is>
           <t>Online / TBA</t>
         </is>
       </c>
-      <c r="B23" s="10" t="inlineStr">
+      <c r="B23" s="11" t="inlineStr">
         <is>
           <t>MATH 0903-TC1, MATH 1113-TC1</t>
         </is>
@@ -1242,16 +1245,13 @@
     </row>
   </sheetData>
   <autoFilter ref="A2:F20"/>
-  <mergeCells count="10">
+  <mergeCells count="7">
     <mergeCell ref="B9:B10"/>
     <mergeCell ref="D9:D10"/>
     <mergeCell ref="F9:F10"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="D7:D8"/>
-    <mergeCell ref="B7:B8"/>
     <mergeCell ref="B23:F23"/>
-    <mergeCell ref="F7:F8"/>
-    <mergeCell ref="C6:C8"/>
+    <mergeCell ref="C9:C11"/>
     <mergeCell ref="E9:E11"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1369,11 +1369,29 @@
           <t>10:00 AM</t>
         </is>
       </c>
-      <c r="B7" s="4" t="n"/>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>MATH 1003-004
+Corley 267
+10:00 AM-10:50 AM</t>
+        </is>
+      </c>
       <c r="C7" s="4" t="n"/>
-      <c r="D7" s="4" t="n"/>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>MATH 1003-004
+Corley 267
+10:00 AM-10:50 AM</t>
+        </is>
+      </c>
       <c r="E7" s="4" t="n"/>
-      <c r="F7" s="4" t="n"/>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>MATH 1003-004
+Corley 267
+10:00 AM-10:50 AM</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="18" customHeight="1">
       <c r="A8" s="3" t="inlineStr">
@@ -1381,11 +1399,11 @@
           <t>10:30 AM</t>
         </is>
       </c>
-      <c r="B8" s="4" t="n"/>
+      <c r="B8" s="6" t="n"/>
       <c r="C8" s="4" t="n"/>
-      <c r="D8" s="4" t="n"/>
+      <c r="D8" s="6" t="n"/>
       <c r="E8" s="4" t="n"/>
-      <c r="F8" s="4" t="n"/>
+      <c r="F8" s="6" t="n"/>
     </row>
     <row r="9" ht="18" customHeight="1">
       <c r="A9" s="3" t="inlineStr">
@@ -1393,27 +1411,27 @@
           <t>11:00 AM</t>
         </is>
       </c>
-      <c r="B9" s="11" t="inlineStr">
+      <c r="B9" s="5" t="inlineStr">
         <is>
           <t>MATH 0803-004
-11:00 AM-11:50 AM
-/ MATH 1003-004</t>
+Corley 267
+11:00 AM-11:50 AM</t>
         </is>
       </c>
       <c r="C9" s="4" t="n"/>
-      <c r="D9" s="11" t="inlineStr">
+      <c r="D9" s="5" t="inlineStr">
         <is>
           <t>MATH 0803-004
-11:00 AM-11:50 AM
-/ MATH 1003-004</t>
+Corley 267
+11:00 AM-11:50 AM</t>
         </is>
       </c>
       <c r="E9" s="4" t="n"/>
-      <c r="F9" s="11" t="inlineStr">
+      <c r="F9" s="5" t="inlineStr">
         <is>
           <t>MATH 0803-004
-11:00 AM-11:50 AM
-/ MATH 1003-004</t>
+Corley 267
+11:00 AM-11:50 AM</t>
         </is>
       </c>
     </row>
@@ -1551,11 +1569,14 @@
     </row>
   </sheetData>
   <autoFilter ref="A2:F20"/>
-  <mergeCells count="4">
+  <mergeCells count="7">
     <mergeCell ref="B9:B10"/>
     <mergeCell ref="D9:D10"/>
+    <mergeCell ref="F9:F10"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="F9:F10"/>
+    <mergeCell ref="D7:D8"/>
+    <mergeCell ref="B7:B8"/>
+    <mergeCell ref="F7:F8"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>
@@ -1625,9 +1646,21 @@
         </is>
       </c>
       <c r="B3" s="4" t="n"/>
-      <c r="C3" s="4" t="n"/>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>MATH 1113-006
+Corley 102
+8:00 AM-9:20 AM</t>
+        </is>
+      </c>
       <c r="D3" s="4" t="n"/>
-      <c r="E3" s="4" t="n"/>
+      <c r="E3" s="5" t="inlineStr">
+        <is>
+          <t>MATH 1113-006
+Corley 102
+8:00 AM-9:20 AM</t>
+        </is>
+      </c>
       <c r="F3" s="4" t="n"/>
     </row>
     <row r="4" ht="18" customHeight="1">
@@ -1637,9 +1670,9 @@
         </is>
       </c>
       <c r="B4" s="4" t="n"/>
-      <c r="C4" s="4" t="n"/>
+      <c r="C4" s="8" t="n"/>
       <c r="D4" s="4" t="n"/>
-      <c r="E4" s="4" t="n"/>
+      <c r="E4" s="8" t="n"/>
       <c r="F4" s="4" t="n"/>
     </row>
     <row r="5" ht="18" customHeight="1">
@@ -1648,23 +1681,23 @@
           <t>9:00 AM</t>
         </is>
       </c>
-      <c r="B5" s="7" t="inlineStr">
+      <c r="B5" s="13" t="inlineStr">
         <is>
           <t>MATH 2043-001
 Corley 102
 9:00 AM-9:50 AM</t>
         </is>
       </c>
-      <c r="C5" s="4" t="n"/>
-      <c r="D5" s="7" t="inlineStr">
+      <c r="C5" s="6" t="n"/>
+      <c r="D5" s="13" t="inlineStr">
         <is>
           <t>MATH 2043-001
 Corley 102
 9:00 AM-9:50 AM</t>
         </is>
       </c>
-      <c r="E5" s="4" t="n"/>
-      <c r="F5" s="7" t="inlineStr">
+      <c r="E5" s="6" t="n"/>
+      <c r="F5" s="13" t="inlineStr">
         <is>
           <t>MATH 2043-001
 Corley 102
@@ -1679,21 +1712,9 @@
         </is>
       </c>
       <c r="B6" s="6" t="n"/>
-      <c r="C6" s="11" t="inlineStr">
-        <is>
-          <t>MATH 1113-006
-Corley 104
-9:30 AM-10:50 AM</t>
-        </is>
-      </c>
+      <c r="C6" s="4" t="n"/>
       <c r="D6" s="6" t="n"/>
-      <c r="E6" s="11" t="inlineStr">
-        <is>
-          <t>MATH 1113-006
-Corley 104
-9:30 AM-10:50 AM</t>
-        </is>
-      </c>
+      <c r="E6" s="4" t="n"/>
       <c r="F6" s="6" t="n"/>
     </row>
     <row r="7" ht="18" customHeight="1">
@@ -1702,23 +1723,23 @@
           <t>10:00 AM</t>
         </is>
       </c>
-      <c r="B7" s="5" t="inlineStr">
+      <c r="B7" s="7" t="inlineStr">
         <is>
           <t>MATH 2033-001
 Corley 102
 10:00 AM-10:50 AM</t>
         </is>
       </c>
-      <c r="C7" s="8" t="n"/>
-      <c r="D7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="n"/>
+      <c r="D7" s="7" t="inlineStr">
         <is>
           <t>MATH 2033-001
 Corley 102
 10:00 AM-10:50 AM</t>
         </is>
       </c>
-      <c r="E7" s="8" t="n"/>
-      <c r="F7" s="5" t="inlineStr">
+      <c r="E7" s="4" t="n"/>
+      <c r="F7" s="7" t="inlineStr">
         <is>
           <t>MATH 2033-001
 Corley 102
@@ -1733,9 +1754,9 @@
         </is>
       </c>
       <c r="B8" s="6" t="n"/>
-      <c r="C8" s="6" t="n"/>
+      <c r="C8" s="4" t="n"/>
       <c r="D8" s="6" t="n"/>
-      <c r="E8" s="6" t="n"/>
+      <c r="E8" s="4" t="n"/>
       <c r="F8" s="6" t="n"/>
     </row>
     <row r="9" ht="18" customHeight="1">
@@ -1745,7 +1766,7 @@
         </is>
       </c>
       <c r="B9" s="4" t="n"/>
-      <c r="C9" s="12" t="inlineStr">
+      <c r="C9" s="9" t="inlineStr">
         <is>
           <t>MATH 3033-001
 Corley 102
@@ -1753,7 +1774,7 @@
         </is>
       </c>
       <c r="D9" s="4" t="n"/>
-      <c r="E9" s="12" t="inlineStr">
+      <c r="E9" s="9" t="inlineStr">
         <is>
           <t>MATH 3033-001
 Corley 102
@@ -1895,12 +1916,12 @@
       <c r="F20" s="4" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="9" t="inlineStr">
+      <c r="A23" s="10" t="inlineStr">
         <is>
           <t>Online / TBA</t>
         </is>
       </c>
-      <c r="B23" s="10" t="inlineStr">
+      <c r="B23" s="11" t="inlineStr">
         <is>
           <t>MATH 2043-TC1</t>
         </is>
@@ -1911,14 +1932,14 @@
   <mergeCells count="12">
     <mergeCell ref="E9:E11"/>
     <mergeCell ref="A1:F1"/>
+    <mergeCell ref="C3:C5"/>
     <mergeCell ref="D7:D8"/>
+    <mergeCell ref="E3:E5"/>
     <mergeCell ref="B7:B8"/>
     <mergeCell ref="C9:C11"/>
     <mergeCell ref="B23:F23"/>
     <mergeCell ref="F7:F8"/>
     <mergeCell ref="F5:F6"/>
-    <mergeCell ref="C6:C8"/>
-    <mergeCell ref="E6:E8"/>
     <mergeCell ref="B5:B6"/>
     <mergeCell ref="D5:D6"/>
   </mergeCells>
@@ -1991,24 +2012,36 @@
       </c>
       <c r="B3" s="7" t="inlineStr">
         <is>
-          <t>MATH 1003-006
-Rothwell 221
+          <t>MATH 0903-002
+Corley 104
 8:00 AM-8:50 AM</t>
         </is>
       </c>
-      <c r="C3" s="4" t="n"/>
+      <c r="C3" s="7" t="inlineStr">
+        <is>
+          <t>MATH 1113-002
+Corley 104
+8:00 AM-9:20 AM</t>
+        </is>
+      </c>
       <c r="D3" s="7" t="inlineStr">
         <is>
-          <t>MATH 1003-006
-Rothwell 221
+          <t>MATH 0903-002
+Corley 104
 8:00 AM-8:50 AM</t>
         </is>
       </c>
-      <c r="E3" s="4" t="n"/>
+      <c r="E3" s="7" t="inlineStr">
+        <is>
+          <t>MATH 1113-002
+Corley 104
+8:00 AM-9:20 AM</t>
+        </is>
+      </c>
       <c r="F3" s="7" t="inlineStr">
         <is>
-          <t>MATH 1003-006
-Rothwell 221
+          <t>MATH 0903-002
+Corley 104
 8:00 AM-8:50 AM</t>
         </is>
       </c>
@@ -2020,9 +2053,9 @@
         </is>
       </c>
       <c r="B4" s="6" t="n"/>
-      <c r="C4" s="4" t="n"/>
+      <c r="C4" s="8" t="n"/>
       <c r="D4" s="6" t="n"/>
-      <c r="E4" s="4" t="n"/>
+      <c r="E4" s="8" t="n"/>
       <c r="F4" s="6" t="n"/>
     </row>
     <row r="5" ht="18" customHeight="1">
@@ -2031,26 +2064,26 @@
           <t>9:00 AM</t>
         </is>
       </c>
-      <c r="B5" s="11" t="inlineStr">
+      <c r="B5" s="5" t="inlineStr">
         <is>
           <t>MATH 1003-001
-Corley 103
+Corley 267
 9:00 AM-9:50 AM</t>
         </is>
       </c>
-      <c r="C5" s="4" t="n"/>
-      <c r="D5" s="11" t="inlineStr">
+      <c r="C5" s="6" t="n"/>
+      <c r="D5" s="5" t="inlineStr">
         <is>
           <t>MATH 1003-001
-Corley 103
+Corley 267
 9:00 AM-9:50 AM</t>
         </is>
       </c>
-      <c r="E5" s="4" t="n"/>
-      <c r="F5" s="11" t="inlineStr">
+      <c r="E5" s="6" t="n"/>
+      <c r="F5" s="5" t="inlineStr">
         <is>
           <t>MATH 1003-001
-Corley 103
+Corley 267
 9:00 AM-9:50 AM</t>
         </is>
       </c>
@@ -2062,7 +2095,7 @@
         </is>
       </c>
       <c r="B6" s="6" t="n"/>
-      <c r="C6" s="11" t="inlineStr">
+      <c r="C6" s="5" t="inlineStr">
         <is>
           <t>MATH 0803-001
 Corley 103
@@ -2070,7 +2103,7 @@
         </is>
       </c>
       <c r="D6" s="6" t="n"/>
-      <c r="E6" s="11" t="inlineStr">
+      <c r="E6" s="5" t="inlineStr">
         <is>
           <t>MATH 0803-001
 Corley 103
@@ -2085,7 +2118,7 @@
           <t>10:00 AM</t>
         </is>
       </c>
-      <c r="B7" s="5" t="inlineStr">
+      <c r="B7" s="13" t="inlineStr">
         <is>
           <t>MATH 1003-005
 Corley 104
@@ -2093,7 +2126,7 @@
         </is>
       </c>
       <c r="C7" s="8" t="n"/>
-      <c r="D7" s="5" t="inlineStr">
+      <c r="D7" s="13" t="inlineStr">
         <is>
           <t>MATH 1003-005
 Corley 104
@@ -2101,7 +2134,7 @@
         </is>
       </c>
       <c r="E7" s="8" t="n"/>
-      <c r="F7" s="5" t="inlineStr">
+      <c r="F7" s="13" t="inlineStr">
         <is>
           <t>MATH 1003-005
 Corley 104
@@ -2175,29 +2208,11 @@
           <t>1:00 PM</t>
         </is>
       </c>
-      <c r="B13" s="13" t="inlineStr">
-        <is>
-          <t>MATH 1003-007
-Corley 267
-1:00 PM-1:50 PM</t>
-        </is>
-      </c>
+      <c r="B13" s="4" t="n"/>
       <c r="C13" s="4" t="n"/>
-      <c r="D13" s="13" t="inlineStr">
-        <is>
-          <t>MATH 1003-007
-Corley 267
-1:00 PM-1:50 PM</t>
-        </is>
-      </c>
+      <c r="D13" s="4" t="n"/>
       <c r="E13" s="4" t="n"/>
-      <c r="F13" s="13" t="inlineStr">
-        <is>
-          <t>MATH 1003-007
-Corley 267
-1:00 PM-1:50 PM</t>
-        </is>
-      </c>
+      <c r="F13" s="4" t="n"/>
     </row>
     <row r="14" ht="18" customHeight="1">
       <c r="A14" s="3" t="inlineStr">
@@ -2205,11 +2220,11 @@
           <t>1:30 PM</t>
         </is>
       </c>
-      <c r="B14" s="6" t="n"/>
+      <c r="B14" s="4" t="n"/>
       <c r="C14" s="4" t="n"/>
-      <c r="D14" s="6" t="n"/>
+      <c r="D14" s="4" t="n"/>
       <c r="E14" s="4" t="n"/>
-      <c r="F14" s="6" t="n"/>
+      <c r="F14" s="4" t="n"/>
     </row>
     <row r="15" ht="18" customHeight="1">
       <c r="A15" s="3" t="inlineStr">
@@ -2285,15 +2300,14 @@
     </row>
   </sheetData>
   <autoFilter ref="A2:F20"/>
-  <mergeCells count="15">
-    <mergeCell ref="F13:F14"/>
-    <mergeCell ref="B13:B14"/>
+  <mergeCells count="14">
     <mergeCell ref="B3:B4"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="D13:D14"/>
+    <mergeCell ref="C3:C5"/>
     <mergeCell ref="D7:D8"/>
     <mergeCell ref="F3:F4"/>
     <mergeCell ref="D3:D4"/>
+    <mergeCell ref="E3:E5"/>
     <mergeCell ref="B7:B8"/>
     <mergeCell ref="F7:F8"/>
     <mergeCell ref="F5:F6"/>
@@ -2369,11 +2383,29 @@
           <t>8:00 AM</t>
         </is>
       </c>
-      <c r="B3" s="4" t="n"/>
+      <c r="B3" s="9" t="inlineStr">
+        <is>
+          <t>STAT 3113-001
+Rothwell 213
+8:00 AM-8:50 AM</t>
+        </is>
+      </c>
       <c r="C3" s="4" t="n"/>
-      <c r="D3" s="4" t="n"/>
+      <c r="D3" s="9" t="inlineStr">
+        <is>
+          <t>STAT 3113-001
+Rothwell 213
+8:00 AM-8:50 AM</t>
+        </is>
+      </c>
       <c r="E3" s="4" t="n"/>
-      <c r="F3" s="4" t="n"/>
+      <c r="F3" s="9" t="inlineStr">
+        <is>
+          <t>STAT 3113-001
+Rothwell 213
+8:00 AM-8:50 AM</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="18" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
@@ -2381,11 +2413,11 @@
           <t>8:30 AM</t>
         </is>
       </c>
-      <c r="B4" s="4" t="n"/>
+      <c r="B4" s="6" t="n"/>
       <c r="C4" s="4" t="n"/>
-      <c r="D4" s="4" t="n"/>
+      <c r="D4" s="6" t="n"/>
       <c r="E4" s="4" t="n"/>
-      <c r="F4" s="4" t="n"/>
+      <c r="F4" s="6" t="n"/>
     </row>
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
@@ -2393,26 +2425,26 @@
           <t>9:00 AM</t>
         </is>
       </c>
-      <c r="B5" s="7" t="inlineStr">
-        <is>
-          <t>MATH 4003-001
-Rothwell 206
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>MATH 2924-003
+Rothwell 306
 9:00 AM-9:50 AM</t>
         </is>
       </c>
       <c r="C5" s="4" t="n"/>
-      <c r="D5" s="7" t="inlineStr">
-        <is>
-          <t>MATH 4003-001
-Rothwell 206
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>MATH 2924-003
+Rothwell 306
 9:00 AM-9:50 AM</t>
         </is>
       </c>
       <c r="E5" s="4" t="n"/>
-      <c r="F5" s="7" t="inlineStr">
-        <is>
-          <t>MATH 4003-001
-Rothwell 206
+      <c r="F5" s="5" t="inlineStr">
+        <is>
+          <t>MATH 2924-003
+Rothwell 306
 9:00 AM-9:50 AM</t>
         </is>
       </c>
@@ -2426,7 +2458,13 @@
       <c r="B6" s="6" t="n"/>
       <c r="C6" s="4" t="n"/>
       <c r="D6" s="6" t="n"/>
-      <c r="E6" s="4" t="n"/>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>MATH 2924-003
+Rothwell 206
+9:30 AM-10:50 AM</t>
+        </is>
+      </c>
       <c r="F6" s="6" t="n"/>
     </row>
     <row r="7" ht="18" customHeight="1">
@@ -2435,7 +2473,7 @@
           <t>10:00 AM</t>
         </is>
       </c>
-      <c r="B7" s="11" t="inlineStr">
+      <c r="B7" s="7" t="inlineStr">
         <is>
           <t>MATH 3243-001
 Rothwell 206
@@ -2443,15 +2481,15 @@
         </is>
       </c>
       <c r="C7" s="4" t="n"/>
-      <c r="D7" s="11" t="inlineStr">
+      <c r="D7" s="7" t="inlineStr">
         <is>
           <t>MATH 3243-001
 Rothwell 206
 10:00 AM-10:50 AM</t>
         </is>
       </c>
-      <c r="E7" s="4" t="n"/>
-      <c r="F7" s="11" t="inlineStr">
+      <c r="E7" s="8" t="n"/>
+      <c r="F7" s="7" t="inlineStr">
         <is>
           <t>MATH 3243-001
 Rothwell 206
@@ -2468,7 +2506,7 @@
       <c r="B8" s="6" t="n"/>
       <c r="C8" s="4" t="n"/>
       <c r="D8" s="6" t="n"/>
-      <c r="E8" s="4" t="n"/>
+      <c r="E8" s="6" t="n"/>
       <c r="F8" s="6" t="n"/>
     </row>
     <row r="9" ht="18" customHeight="1">
@@ -2477,32 +2515,32 @@
           <t>11:00 AM</t>
         </is>
       </c>
-      <c r="B9" s="12" t="inlineStr">
-        <is>
-          <t>STAT 3113-001
-Rothwell 213
+      <c r="B9" s="13" t="inlineStr">
+        <is>
+          <t>MATH 4003-001
+Rothwell 206
 11:00 AM-11:50 AM</t>
         </is>
       </c>
-      <c r="C9" s="13" t="inlineStr">
+      <c r="C9" s="12" t="inlineStr">
         <is>
           <t>MATH 4971-001
 Corley 101
 11:00 AM-12:20 PM</t>
         </is>
       </c>
-      <c r="D9" s="12" t="inlineStr">
-        <is>
-          <t>STAT 3113-001
-Rothwell 213
+      <c r="D9" s="13" t="inlineStr">
+        <is>
+          <t>MATH 4003-001
+Rothwell 206
 11:00 AM-11:50 AM</t>
         </is>
       </c>
       <c r="E9" s="4" t="n"/>
-      <c r="F9" s="12" t="inlineStr">
-        <is>
-          <t>STAT 3113-001
-Rothwell 213
+      <c r="F9" s="13" t="inlineStr">
+        <is>
+          <t>MATH 4003-001
+Rothwell 206
 11:00 AM-11:50 AM</t>
         </is>
       </c>
@@ -2549,29 +2587,11 @@
           <t>1:00 PM</t>
         </is>
       </c>
-      <c r="B13" s="5" t="inlineStr">
-        <is>
-          <t>MATH 3243-002
-Rothwell 212
-1:00 PM-1:50 PM</t>
-        </is>
-      </c>
+      <c r="B13" s="4" t="n"/>
       <c r="C13" s="4" t="n"/>
-      <c r="D13" s="5" t="inlineStr">
-        <is>
-          <t>MATH 3243-002
-Rothwell 212
-1:00 PM-1:50 PM</t>
-        </is>
-      </c>
+      <c r="D13" s="4" t="n"/>
       <c r="E13" s="4" t="n"/>
-      <c r="F13" s="5" t="inlineStr">
-        <is>
-          <t>MATH 3243-002
-Rothwell 212
-1:00 PM-1:50 PM</t>
-        </is>
-      </c>
+      <c r="F13" s="4" t="n"/>
     </row>
     <row r="14" ht="18" customHeight="1">
       <c r="A14" s="3" t="inlineStr">
@@ -2579,11 +2599,11 @@
           <t>1:30 PM</t>
         </is>
       </c>
-      <c r="B14" s="6" t="n"/>
+      <c r="B14" s="4" t="n"/>
       <c r="C14" s="4" t="n"/>
-      <c r="D14" s="6" t="n"/>
+      <c r="D14" s="4" t="n"/>
       <c r="E14" s="4" t="n"/>
-      <c r="F14" s="6" t="n"/>
+      <c r="F14" s="4" t="n"/>
     </row>
     <row r="15" ht="18" customHeight="1">
       <c r="A15" s="3" t="inlineStr">
@@ -2659,19 +2679,20 @@
     </row>
   </sheetData>
   <autoFilter ref="A2:F20"/>
-  <mergeCells count="14">
-    <mergeCell ref="F13:F14"/>
+  <mergeCells count="15">
     <mergeCell ref="B9:B10"/>
     <mergeCell ref="D9:D10"/>
     <mergeCell ref="F9:F10"/>
-    <mergeCell ref="B13:B14"/>
+    <mergeCell ref="B3:B4"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="D13:D14"/>
     <mergeCell ref="D7:D8"/>
+    <mergeCell ref="F3:F4"/>
+    <mergeCell ref="D3:D4"/>
     <mergeCell ref="B7:B8"/>
     <mergeCell ref="C9:C11"/>
     <mergeCell ref="F7:F8"/>
     <mergeCell ref="F5:F6"/>
+    <mergeCell ref="E6:E8"/>
     <mergeCell ref="B5:B6"/>
     <mergeCell ref="D5:D6"/>
   </mergeCells>
@@ -2742,11 +2763,29 @@
           <t>8:00 AM</t>
         </is>
       </c>
-      <c r="B3" s="4" t="n"/>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>MATH 1113-F01
+Corley 269
+8:00 AM-8:50 AM</t>
+        </is>
+      </c>
       <c r="C3" s="4" t="n"/>
-      <c r="D3" s="4" t="n"/>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>MATH 1113-F01
+Corley 269
+8:00 AM-8:50 AM</t>
+        </is>
+      </c>
       <c r="E3" s="4" t="n"/>
-      <c r="F3" s="4" t="n"/>
+      <c r="F3" s="5" t="inlineStr">
+        <is>
+          <t>MATH 1113-F01
+Corley 269
+8:00 AM-8:50 AM</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="18" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
@@ -2754,11 +2793,11 @@
           <t>8:30 AM</t>
         </is>
       </c>
-      <c r="B4" s="4" t="n"/>
+      <c r="B4" s="6" t="n"/>
       <c r="C4" s="4" t="n"/>
-      <c r="D4" s="4" t="n"/>
+      <c r="D4" s="6" t="n"/>
       <c r="E4" s="4" t="n"/>
-      <c r="F4" s="4" t="n"/>
+      <c r="F4" s="6" t="n"/>
     </row>
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
@@ -2779,7 +2818,13 @@
         </is>
       </c>
       <c r="B6" s="4" t="n"/>
-      <c r="C6" s="4" t="n"/>
+      <c r="C6" s="12" t="inlineStr">
+        <is>
+          <t>MATH 2934-001
+Rothwell 207
+9:30 AM-10:50 AM</t>
+        </is>
+      </c>
       <c r="D6" s="4" t="n"/>
       <c r="E6" s="4" t="n"/>
       <c r="F6" s="4" t="n"/>
@@ -2790,26 +2835,26 @@
           <t>10:00 AM</t>
         </is>
       </c>
-      <c r="B7" s="11" t="inlineStr">
-        <is>
-          <t>MATH 1113-F01
-Corley 269
+      <c r="B7" s="12" t="inlineStr">
+        <is>
+          <t>MATH 2934-001
+Rothwell 207
 10:00 AM-10:50 AM</t>
         </is>
       </c>
-      <c r="C7" s="4" t="n"/>
-      <c r="D7" s="11" t="inlineStr">
-        <is>
-          <t>MATH 1113-F01
-Corley 269
+      <c r="C7" s="8" t="n"/>
+      <c r="D7" s="12" t="inlineStr">
+        <is>
+          <t>MATH 2934-001
+Rothwell 207
 10:00 AM-10:50 AM</t>
         </is>
       </c>
       <c r="E7" s="4" t="n"/>
-      <c r="F7" s="11" t="inlineStr">
-        <is>
-          <t>MATH 1113-F01
-Corley 269
+      <c r="F7" s="12" t="inlineStr">
+        <is>
+          <t>MATH 2934-001
+Rothwell 207
 10:00 AM-10:50 AM</t>
         </is>
       </c>
@@ -2821,7 +2866,7 @@
         </is>
       </c>
       <c r="B8" s="6" t="n"/>
-      <c r="C8" s="4" t="n"/>
+      <c r="C8" s="6" t="n"/>
       <c r="D8" s="6" t="n"/>
       <c r="E8" s="4" t="n"/>
       <c r="F8" s="6" t="n"/>
@@ -2832,41 +2877,11 @@
           <t>11:00 AM</t>
         </is>
       </c>
-      <c r="B9" s="13" t="inlineStr">
-        <is>
-          <t>MATH 1113-001
-Corley 104
-11:00 AM-11:50 AM</t>
-        </is>
-      </c>
-      <c r="C9" s="13" t="inlineStr">
-        <is>
-          <t>MATH 0903-001
-Corley 104
-11:00 AM-12:20 PM</t>
-        </is>
-      </c>
-      <c r="D9" s="13" t="inlineStr">
-        <is>
-          <t>MATH 1113-001
-Corley 104
-11:00 AM-11:50 AM</t>
-        </is>
-      </c>
-      <c r="E9" s="13" t="inlineStr">
-        <is>
-          <t>MATH 0903-001
-Corley 104
-11:00 AM-12:20 PM</t>
-        </is>
-      </c>
-      <c r="F9" s="13" t="inlineStr">
-        <is>
-          <t>MATH 1113-001
-Corley 104
-11:00 AM-11:50 AM</t>
-        </is>
-      </c>
+      <c r="B9" s="4" t="n"/>
+      <c r="C9" s="4" t="n"/>
+      <c r="D9" s="4" t="n"/>
+      <c r="E9" s="4" t="n"/>
+      <c r="F9" s="4" t="n"/>
     </row>
     <row r="10" ht="18" customHeight="1">
       <c r="A10" s="3" t="inlineStr">
@@ -2874,11 +2889,11 @@
           <t>11:30 AM</t>
         </is>
       </c>
-      <c r="B10" s="6" t="n"/>
-      <c r="C10" s="8" t="n"/>
-      <c r="D10" s="6" t="n"/>
-      <c r="E10" s="8" t="n"/>
-      <c r="F10" s="6" t="n"/>
+      <c r="B10" s="4" t="n"/>
+      <c r="C10" s="4" t="n"/>
+      <c r="D10" s="4" t="n"/>
+      <c r="E10" s="4" t="n"/>
+      <c r="F10" s="4" t="n"/>
     </row>
     <row r="11" ht="18" customHeight="1">
       <c r="A11" s="3" t="inlineStr">
@@ -2887,9 +2902,9 @@
         </is>
       </c>
       <c r="B11" s="4" t="n"/>
-      <c r="C11" s="6" t="n"/>
+      <c r="C11" s="4" t="n"/>
       <c r="D11" s="4" t="n"/>
-      <c r="E11" s="6" t="n"/>
+      <c r="E11" s="4" t="n"/>
       <c r="F11" s="4" t="n"/>
     </row>
     <row r="12" ht="18" customHeight="1">
@@ -2917,7 +2932,13 @@
 1:00 PM-1:50 PM</t>
         </is>
       </c>
-      <c r="C13" s="4" t="n"/>
+      <c r="C13" s="13" t="inlineStr">
+        <is>
+          <t>MATH 2924-002
+Rothwell 206
+1:00 PM-2:20 PM</t>
+        </is>
+      </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
           <t>MATH 2924-001
@@ -2947,7 +2968,7 @@
         </is>
       </c>
       <c r="B14" s="6" t="n"/>
-      <c r="C14" s="4" t="n"/>
+      <c r="C14" s="8" t="n"/>
       <c r="D14" s="6" t="n"/>
       <c r="E14" s="8" t="n"/>
       <c r="F14" s="6" t="n"/>
@@ -2958,26 +2979,26 @@
           <t>2:00 PM</t>
         </is>
       </c>
-      <c r="B15" s="5" t="inlineStr">
-        <is>
-          <t>MATH 2914-003
-Corley 101
+      <c r="B15" s="13" t="inlineStr">
+        <is>
+          <t>MATH 2924-002
+Rothwell 206
 2:00 PM-2:50 PM</t>
         </is>
       </c>
-      <c r="C15" s="4" t="n"/>
-      <c r="D15" s="5" t="inlineStr">
-        <is>
-          <t>MATH 2914-003
-Corley 101
+      <c r="C15" s="6" t="n"/>
+      <c r="D15" s="13" t="inlineStr">
+        <is>
+          <t>MATH 2924-002
+Rothwell 206
 2:00 PM-2:50 PM</t>
         </is>
       </c>
       <c r="E15" s="6" t="n"/>
-      <c r="F15" s="5" t="inlineStr">
-        <is>
-          <t>MATH 2914-003
-Corley 101
+      <c r="F15" s="13" t="inlineStr">
+        <is>
+          <t>MATH 2924-002
+Rothwell 206
 2:00 PM-2:50 PM</t>
         </is>
       </c>
@@ -2991,13 +3012,7 @@
       <c r="B16" s="6" t="n"/>
       <c r="C16" s="4" t="n"/>
       <c r="D16" s="6" t="n"/>
-      <c r="E16" s="5" t="inlineStr">
-        <is>
-          <t>MATH 2914-003
-Corley 268
-2:30 PM-3:50 PM</t>
-        </is>
-      </c>
+      <c r="E16" s="4" t="n"/>
       <c r="F16" s="6" t="n"/>
     </row>
     <row r="17" ht="18" customHeight="1">
@@ -3009,7 +3024,7 @@
       <c r="B17" s="4" t="n"/>
       <c r="C17" s="4" t="n"/>
       <c r="D17" s="4" t="n"/>
-      <c r="E17" s="8" t="n"/>
+      <c r="E17" s="4" t="n"/>
       <c r="F17" s="4" t="n"/>
     </row>
     <row r="18" ht="18" customHeight="1">
@@ -3021,7 +3036,7 @@
       <c r="B18" s="4" t="n"/>
       <c r="C18" s="4" t="n"/>
       <c r="D18" s="4" t="n"/>
-      <c r="E18" s="6" t="n"/>
+      <c r="E18" s="4" t="n"/>
       <c r="F18" s="4" t="n"/>
     </row>
     <row r="19" ht="18" customHeight="1">
@@ -3049,12 +3064,12 @@
       <c r="F20" s="4" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="9" t="inlineStr">
+      <c r="A23" s="10" t="inlineStr">
         <is>
           <t>Online / TBA</t>
         </is>
       </c>
-      <c r="B23" s="10" t="inlineStr">
+      <c r="B23" s="11" t="inlineStr">
         <is>
           <t>MATH 1113-F01</t>
         </is>
@@ -3062,25 +3077,24 @@
     </row>
   </sheetData>
   <autoFilter ref="A2:F20"/>
-  <mergeCells count="18">
+  <mergeCells count="17">
     <mergeCell ref="E13:E15"/>
     <mergeCell ref="F13:F14"/>
-    <mergeCell ref="B9:B10"/>
+    <mergeCell ref="C13:C15"/>
     <mergeCell ref="D15:D16"/>
-    <mergeCell ref="D9:D10"/>
     <mergeCell ref="F15:F16"/>
-    <mergeCell ref="F9:F10"/>
     <mergeCell ref="B13:B14"/>
-    <mergeCell ref="E16:E18"/>
+    <mergeCell ref="B3:B4"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="D13:D14"/>
     <mergeCell ref="D7:D8"/>
+    <mergeCell ref="F3:F4"/>
+    <mergeCell ref="D3:D4"/>
     <mergeCell ref="B7:B8"/>
     <mergeCell ref="B23:F23"/>
     <mergeCell ref="F7:F8"/>
-    <mergeCell ref="C9:C11"/>
+    <mergeCell ref="C6:C8"/>
     <mergeCell ref="B15:B16"/>
-    <mergeCell ref="E9:E11"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>
@@ -3188,7 +3202,7 @@
       <c r="B6" s="4" t="n"/>
       <c r="C6" s="4" t="n"/>
       <c r="D6" s="4" t="n"/>
-      <c r="E6" s="11" t="inlineStr">
+      <c r="E6" s="5" t="inlineStr">
         <is>
           <t>MATH 1914-003
 Corley 102
@@ -3203,7 +3217,7 @@
           <t>10:00 AM</t>
         </is>
       </c>
-      <c r="B7" s="11" t="inlineStr">
+      <c r="B7" s="5" t="inlineStr">
         <is>
           <t>MATH 1914-003
 Corley 268
@@ -3211,7 +3225,7 @@
         </is>
       </c>
       <c r="C7" s="4" t="n"/>
-      <c r="D7" s="11" t="inlineStr">
+      <c r="D7" s="5" t="inlineStr">
         <is>
           <t>MATH 1914-003
 Corley 268
@@ -3219,7 +3233,7 @@
         </is>
       </c>
       <c r="E7" s="8" t="n"/>
-      <c r="F7" s="11" t="inlineStr">
+      <c r="F7" s="5" t="inlineStr">
         <is>
           <t>MATH 1914-003
 Corley 268
@@ -3293,7 +3307,7 @@
           <t>1:00 PM</t>
         </is>
       </c>
-      <c r="B13" s="5" t="inlineStr">
+      <c r="B13" s="7" t="inlineStr">
         <is>
           <t>MATH 0803-003
 Corley 103
@@ -3301,7 +3315,7 @@
         </is>
       </c>
       <c r="C13" s="4" t="n"/>
-      <c r="D13" s="5" t="inlineStr">
+      <c r="D13" s="7" t="inlineStr">
         <is>
           <t>MATH 0803-003
 Corley 103
@@ -3309,7 +3323,7 @@
         </is>
       </c>
       <c r="E13" s="4" t="n"/>
-      <c r="F13" s="5" t="inlineStr">
+      <c r="F13" s="7" t="inlineStr">
         <is>
           <t>MATH 0803-003
 Corley 103
@@ -3335,7 +3349,7 @@
           <t>2:00 PM</t>
         </is>
       </c>
-      <c r="B15" s="5" t="inlineStr">
+      <c r="B15" s="7" t="inlineStr">
         <is>
           <t>MATH 1003-003
 Corley 103
@@ -3343,7 +3357,7 @@
         </is>
       </c>
       <c r="C15" s="4" t="n"/>
-      <c r="D15" s="5" t="inlineStr">
+      <c r="D15" s="7" t="inlineStr">
         <is>
           <t>MATH 1003-003
 Corley 103
@@ -3351,7 +3365,7 @@
         </is>
       </c>
       <c r="E15" s="4" t="n"/>
-      <c r="F15" s="5" t="inlineStr">
+      <c r="F15" s="7" t="inlineStr">
         <is>
           <t>MATH 1003-003
 Corley 103
@@ -3420,12 +3434,12 @@
       <c r="F20" s="4" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="9" t="inlineStr">
+      <c r="A23" s="10" t="inlineStr">
         <is>
           <t>Online / TBA</t>
         </is>
       </c>
-      <c r="B23" s="10" t="inlineStr">
+      <c r="B23" s="11" t="inlineStr">
         <is>
           <t>MATH 1113-TC2</t>
         </is>
@@ -3538,11 +3552,29 @@
           <t>9:00 AM</t>
         </is>
       </c>
-      <c r="B5" s="4" t="n"/>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>MATH 2223-001
+Corley 103
+9:00 AM-9:50 AM</t>
+        </is>
+      </c>
       <c r="C5" s="4" t="n"/>
-      <c r="D5" s="4" t="n"/>
+      <c r="D5" s="7" t="inlineStr">
+        <is>
+          <t>MATH 2223-001
+Corley 103
+9:00 AM-9:50 AM</t>
+        </is>
+      </c>
       <c r="E5" s="4" t="n"/>
-      <c r="F5" s="4" t="n"/>
+      <c r="F5" s="7" t="inlineStr">
+        <is>
+          <t>MATH 2223-001
+Corley 103
+9:00 AM-9:50 AM</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="18" customHeight="1">
       <c r="A6" s="3" t="inlineStr">
@@ -3550,11 +3582,11 @@
           <t>9:30 AM</t>
         </is>
       </c>
-      <c r="B6" s="4" t="n"/>
+      <c r="B6" s="6" t="n"/>
       <c r="C6" s="4" t="n"/>
-      <c r="D6" s="4" t="n"/>
+      <c r="D6" s="6" t="n"/>
       <c r="E6" s="4" t="n"/>
-      <c r="F6" s="4" t="n"/>
+      <c r="F6" s="6" t="n"/>
     </row>
     <row r="7" ht="18" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
@@ -3562,7 +3594,7 @@
           <t>10:00 AM</t>
         </is>
       </c>
-      <c r="B7" s="7" t="inlineStr">
+      <c r="B7" s="12" t="inlineStr">
         <is>
           <t>MATH 2223-003
 Corley 103
@@ -3570,7 +3602,7 @@
         </is>
       </c>
       <c r="C7" s="4" t="n"/>
-      <c r="D7" s="7" t="inlineStr">
+      <c r="D7" s="12" t="inlineStr">
         <is>
           <t>MATH 2223-003
 Corley 103
@@ -3578,7 +3610,7 @@
         </is>
       </c>
       <c r="E7" s="4" t="n"/>
-      <c r="F7" s="7" t="inlineStr">
+      <c r="F7" s="12" t="inlineStr">
         <is>
           <t>MATH 2223-003
 Corley 103
@@ -3604,41 +3636,23 @@
           <t>11:00 AM</t>
         </is>
       </c>
-      <c r="B9" s="11" t="inlineStr">
-        <is>
-          <t>MATH 2223-001
-Corley 103
-11:00 AM-11:50 AM</t>
-        </is>
-      </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="B9" s="4" t="n"/>
+      <c r="C9" s="13" t="inlineStr">
         <is>
           <t>MATH 2223-002
 Corley 103
 11:00 AM-12:20 PM</t>
         </is>
       </c>
-      <c r="D9" s="11" t="inlineStr">
-        <is>
-          <t>MATH 2223-001
-Corley 103
-11:00 AM-11:50 AM</t>
-        </is>
-      </c>
-      <c r="E9" s="5" t="inlineStr">
+      <c r="D9" s="4" t="n"/>
+      <c r="E9" s="13" t="inlineStr">
         <is>
           <t>MATH 2223-002
 Corley 103
 11:00 AM-12:20 PM</t>
         </is>
       </c>
-      <c r="F9" s="11" t="inlineStr">
-        <is>
-          <t>MATH 2223-001
-Corley 103
-11:00 AM-11:50 AM</t>
-        </is>
-      </c>
+      <c r="F9" s="4" t="n"/>
     </row>
     <row r="10" ht="18" customHeight="1">
       <c r="A10" s="3" t="inlineStr">
@@ -3646,11 +3660,11 @@
           <t>11:30 AM</t>
         </is>
       </c>
-      <c r="B10" s="6" t="n"/>
+      <c r="B10" s="4" t="n"/>
       <c r="C10" s="8" t="n"/>
-      <c r="D10" s="6" t="n"/>
+      <c r="D10" s="4" t="n"/>
       <c r="E10" s="8" t="n"/>
-      <c r="F10" s="6" t="n"/>
+      <c r="F10" s="4" t="n"/>
     </row>
     <row r="11" ht="18" customHeight="1">
       <c r="A11" s="3" t="inlineStr">
@@ -3682,29 +3696,11 @@
           <t>1:00 PM</t>
         </is>
       </c>
-      <c r="B13" s="12" t="inlineStr">
-        <is>
-          <t>MATH 2243-001
-Corley 104
-1:00 PM-1:50 PM</t>
-        </is>
-      </c>
+      <c r="B13" s="4" t="n"/>
       <c r="C13" s="4" t="n"/>
-      <c r="D13" s="12" t="inlineStr">
-        <is>
-          <t>MATH 2243-001
-Corley 104
-1:00 PM-1:50 PM</t>
-        </is>
-      </c>
+      <c r="D13" s="4" t="n"/>
       <c r="E13" s="4" t="n"/>
-      <c r="F13" s="12" t="inlineStr">
-        <is>
-          <t>MATH 2243-001
-Corley 104
-1:00 PM-1:50 PM</t>
-        </is>
-      </c>
+      <c r="F13" s="4" t="n"/>
     </row>
     <row r="14" ht="18" customHeight="1">
       <c r="A14" s="3" t="inlineStr">
@@ -3712,11 +3708,11 @@
           <t>1:30 PM</t>
         </is>
       </c>
-      <c r="B14" s="6" t="n"/>
+      <c r="B14" s="4" t="n"/>
       <c r="C14" s="4" t="n"/>
-      <c r="D14" s="6" t="n"/>
+      <c r="D14" s="4" t="n"/>
       <c r="E14" s="4" t="n"/>
-      <c r="F14" s="6" t="n"/>
+      <c r="F14" s="4" t="n"/>
     </row>
     <row r="15" ht="18" customHeight="1">
       <c r="A15" s="3" t="inlineStr">
@@ -3791,33 +3787,30 @@
       <c r="F20" s="4" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="9" t="inlineStr">
+      <c r="A23" s="10" t="inlineStr">
         <is>
           <t>Online / TBA</t>
         </is>
       </c>
-      <c r="B23" s="10" t="inlineStr">
-        <is>
-          <t>MATH 2223-TC1</t>
+      <c r="B23" s="11" t="inlineStr">
+        <is>
+          <t>MATH 1203-TC1, MATH 2223-TC1</t>
         </is>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A2:F20"/>
-  <mergeCells count="13">
-    <mergeCell ref="F13:F14"/>
-    <mergeCell ref="B9:B10"/>
-    <mergeCell ref="D9:D10"/>
-    <mergeCell ref="F9:F10"/>
-    <mergeCell ref="B13:B14"/>
+  <mergeCells count="10">
+    <mergeCell ref="E9:E11"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="D13:D14"/>
     <mergeCell ref="D7:D8"/>
     <mergeCell ref="B7:B8"/>
+    <mergeCell ref="C9:C11"/>
     <mergeCell ref="B23:F23"/>
     <mergeCell ref="F7:F8"/>
-    <mergeCell ref="C9:C11"/>
-    <mergeCell ref="E9:E11"/>
+    <mergeCell ref="F5:F6"/>
+    <mergeCell ref="B5:B6"/>
+    <mergeCell ref="D5:D6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>
@@ -3888,36 +3881,30 @@
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>MATH 0903-002
-Corley 104
+          <t>MATH 1914-001
+Corley 101
 8:00 AM-8:50 AM</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
-        <is>
-          <t>MATH 1113-002
-Corley 104
+      <c r="C3" s="4" t="n"/>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>MATH 1914-001
+Corley 101
+8:00 AM-8:50 AM</t>
+        </is>
+      </c>
+      <c r="E3" s="5" t="inlineStr">
+        <is>
+          <t>MATH 1914-001
+Corley 101
 8:00 AM-9:20 AM</t>
         </is>
       </c>
-      <c r="D3" s="5" t="inlineStr">
-        <is>
-          <t>MATH 0903-002
-Corley 104
-8:00 AM-8:50 AM</t>
-        </is>
-      </c>
-      <c r="E3" s="5" t="inlineStr">
-        <is>
-          <t>MATH 1113-002
-Corley 104
-8:00 AM-9:20 AM</t>
-        </is>
-      </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>MATH 0903-002
-Corley 104
+          <t>MATH 1914-001
+Corley 101
 8:00 AM-8:50 AM</t>
         </is>
       </c>
@@ -3929,7 +3916,7 @@
         </is>
       </c>
       <c r="B4" s="6" t="n"/>
-      <c r="C4" s="8" t="n"/>
+      <c r="C4" s="4" t="n"/>
       <c r="D4" s="6" t="n"/>
       <c r="E4" s="8" t="n"/>
       <c r="F4" s="6" t="n"/>
@@ -3940,15 +3927,15 @@
           <t>9:00 AM</t>
         </is>
       </c>
-      <c r="B5" s="11" t="inlineStr">
+      <c r="B5" s="7" t="inlineStr">
         <is>
           <t>MATH 0803-002
 Ross Pendergraft Library 331
 9:00 AM-9:50 AM</t>
         </is>
       </c>
-      <c r="C5" s="6" t="n"/>
-      <c r="D5" s="11" t="inlineStr">
+      <c r="C5" s="4" t="n"/>
+      <c r="D5" s="7" t="inlineStr">
         <is>
           <t>MATH 0803-002
 Ross Pendergraft Library 331
@@ -3956,7 +3943,7 @@
         </is>
       </c>
       <c r="E5" s="6" t="n"/>
-      <c r="F5" s="11" t="inlineStr">
+      <c r="F5" s="7" t="inlineStr">
         <is>
           <t>MATH 0803-002
 Ross Pendergraft Library 331
@@ -3982,7 +3969,7 @@
           <t>10:00 AM</t>
         </is>
       </c>
-      <c r="B7" s="11" t="inlineStr">
+      <c r="B7" s="7" t="inlineStr">
         <is>
           <t>MATH 1003-002
 Ross Pendergraft Library 331
@@ -3990,7 +3977,7 @@
         </is>
       </c>
       <c r="C7" s="4" t="n"/>
-      <c r="D7" s="11" t="inlineStr">
+      <c r="D7" s="7" t="inlineStr">
         <is>
           <t>MATH 1003-002
 Ross Pendergraft Library 331
@@ -3998,7 +3985,7 @@
         </is>
       </c>
       <c r="E7" s="4" t="n"/>
-      <c r="F7" s="11" t="inlineStr">
+      <c r="F7" s="7" t="inlineStr">
         <is>
           <t>MATH 1003-002
 Ross Pendergraft Library 331
@@ -4072,7 +4059,7 @@
           <t>1:00 PM</t>
         </is>
       </c>
-      <c r="B13" s="7" t="inlineStr">
+      <c r="B13" s="13" t="inlineStr">
         <is>
           <t>MATH 1113-003
 Rothwell 221
@@ -4080,7 +4067,7 @@
         </is>
       </c>
       <c r="C13" s="4" t="n"/>
-      <c r="D13" s="7" t="inlineStr">
+      <c r="D13" s="13" t="inlineStr">
         <is>
           <t>MATH 1113-003
 Rothwell 221
@@ -4088,7 +4075,7 @@
         </is>
       </c>
       <c r="E13" s="4" t="n"/>
-      <c r="F13" s="7" t="inlineStr">
+      <c r="F13" s="13" t="inlineStr">
         <is>
           <t>MATH 1113-003
 Rothwell 221
@@ -4114,7 +4101,7 @@
           <t>2:00 PM</t>
         </is>
       </c>
-      <c r="B15" s="7" t="inlineStr">
+      <c r="B15" s="13" t="inlineStr">
         <is>
           <t>MATH 1110-003
 Rothwell 221
@@ -4122,7 +4109,7 @@
         </is>
       </c>
       <c r="C15" s="4" t="n"/>
-      <c r="D15" s="7" t="inlineStr">
+      <c r="D15" s="13" t="inlineStr">
         <is>
           <t>MATH 1110-003
 Rothwell 221
@@ -4194,13 +4181,12 @@
     </row>
   </sheetData>
   <autoFilter ref="A2:F20"/>
-  <mergeCells count="17">
+  <mergeCells count="16">
     <mergeCell ref="F13:F14"/>
     <mergeCell ref="D15:D16"/>
     <mergeCell ref="B13:B14"/>
     <mergeCell ref="B3:B4"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="C3:C5"/>
     <mergeCell ref="D13:D14"/>
     <mergeCell ref="D7:D8"/>
     <mergeCell ref="F3:F4"/>
@@ -4304,7 +4290,7 @@
           <t>9:00 AM</t>
         </is>
       </c>
-      <c r="B5" s="5" t="inlineStr">
+      <c r="B5" s="7" t="inlineStr">
         <is>
           <t>STAT 3153-001
 Rothwell 207
@@ -4312,7 +4298,7 @@
         </is>
       </c>
       <c r="C5" s="4" t="n"/>
-      <c r="D5" s="5" t="inlineStr">
+      <c r="D5" s="7" t="inlineStr">
         <is>
           <t>STAT 3153-001
 Rothwell 207
@@ -4320,7 +4306,7 @@
         </is>
       </c>
       <c r="E5" s="4" t="n"/>
-      <c r="F5" s="5" t="inlineStr">
+      <c r="F5" s="7" t="inlineStr">
         <is>
           <t>STAT 3153-001
 Rothwell 207
@@ -4370,7 +4356,7 @@
           <t>11:00 AM</t>
         </is>
       </c>
-      <c r="B9" s="7" t="inlineStr">
+      <c r="B9" s="13" t="inlineStr">
         <is>
           <t>STAT 3153-002
 Corley 102
@@ -4378,7 +4364,7 @@
         </is>
       </c>
       <c r="C9" s="4" t="n"/>
-      <c r="D9" s="7" t="inlineStr">
+      <c r="D9" s="13" t="inlineStr">
         <is>
           <t>STAT 3153-002
 Corley 102
@@ -4386,7 +4372,7 @@
         </is>
       </c>
       <c r="E9" s="4" t="n"/>
-      <c r="F9" s="7" t="inlineStr">
+      <c r="F9" s="13" t="inlineStr">
         <is>
           <t>STAT 3153-002
 Corley 102
@@ -4436,7 +4422,7 @@
           <t>1:00 PM</t>
         </is>
       </c>
-      <c r="B13" s="13" t="inlineStr">
+      <c r="B13" s="12" t="inlineStr">
         <is>
           <t>STAT 3183-001
 Rothwell 213
@@ -4444,7 +4430,7 @@
         </is>
       </c>
       <c r="C13" s="4" t="n"/>
-      <c r="D13" s="13" t="inlineStr">
+      <c r="D13" s="12" t="inlineStr">
         <is>
           <t>STAT 3183-001
 Rothwell 213
@@ -4452,7 +4438,7 @@
         </is>
       </c>
       <c r="E13" s="4" t="n"/>
-      <c r="F13" s="13" t="inlineStr">
+      <c r="F13" s="12" t="inlineStr">
         <is>
           <t>STAT 3183-001
 Rothwell 213
@@ -4545,12 +4531,12 @@
       <c r="F20" s="4" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="9" t="inlineStr">
+      <c r="A23" s="10" t="inlineStr">
         <is>
           <t>Online / TBA</t>
         </is>
       </c>
-      <c r="B23" s="10" t="inlineStr">
+      <c r="B23" s="11" t="inlineStr">
         <is>
           <t>MATH 5173-TC1, STAT 4173-TC1</t>
         </is>
@@ -4582,7 +4568,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F23"/>
+  <dimension ref="A1:F20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -4638,29 +4624,11 @@
           <t>8:00 AM</t>
         </is>
       </c>
-      <c r="B3" s="11" t="inlineStr">
-        <is>
-          <t>MATH 1914-001
-Corley 101
-8:00 AM-8:50 AM</t>
-        </is>
-      </c>
+      <c r="B3" s="4" t="n"/>
       <c r="C3" s="4" t="n"/>
-      <c r="D3" s="11" t="inlineStr">
-        <is>
-          <t>MATH 1914-001
-Corley 101
-8:00 AM-8:50 AM</t>
-        </is>
-      </c>
+      <c r="D3" s="4" t="n"/>
       <c r="E3" s="4" t="n"/>
-      <c r="F3" s="11" t="inlineStr">
-        <is>
-          <t>MATH 1914-001
-Corley 101
-8:00 AM-8:50 AM</t>
-        </is>
-      </c>
+      <c r="F3" s="4" t="n"/>
     </row>
     <row r="4" ht="18" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
@@ -4668,11 +4636,11 @@
           <t>8:30 AM</t>
         </is>
       </c>
-      <c r="B4" s="6" t="n"/>
+      <c r="B4" s="4" t="n"/>
       <c r="C4" s="4" t="n"/>
-      <c r="D4" s="6" t="n"/>
+      <c r="D4" s="4" t="n"/>
       <c r="E4" s="4" t="n"/>
-      <c r="F4" s="6" t="n"/>
+      <c r="F4" s="4" t="n"/>
     </row>
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
@@ -4711,17 +4679,17 @@
         </is>
       </c>
       <c r="B6" s="6" t="n"/>
-      <c r="C6" s="11" t="inlineStr">
-        <is>
-          <t>MATH 1914-001
+      <c r="C6" s="12" t="inlineStr">
+        <is>
+          <t>MATH 2703-002
 Corley 101
 9:30 AM-10:50 AM</t>
         </is>
       </c>
       <c r="D6" s="6" t="n"/>
-      <c r="E6" s="5" t="inlineStr">
-        <is>
-          <t>MATH 2914-001
+      <c r="E6" s="12" t="inlineStr">
+        <is>
+          <t>MATH 2703-002
 Corley 101
 9:30 AM-10:50 AM</t>
         </is>
@@ -4734,11 +4702,29 @@
           <t>10:00 AM</t>
         </is>
       </c>
-      <c r="B7" s="4" t="n"/>
+      <c r="B7" s="13" t="inlineStr">
+        <is>
+          <t>MATH 2703-001
+Corley 101
+10:00 AM-10:50 AM</t>
+        </is>
+      </c>
       <c r="C7" s="8" t="n"/>
-      <c r="D7" s="4" t="n"/>
+      <c r="D7" s="13" t="inlineStr">
+        <is>
+          <t>MATH 2703-001
+Corley 101
+10:00 AM-10:50 AM</t>
+        </is>
+      </c>
       <c r="E7" s="8" t="n"/>
-      <c r="F7" s="4" t="n"/>
+      <c r="F7" s="13" t="inlineStr">
+        <is>
+          <t>MATH 2703-001
+Corley 101
+10:00 AM-10:50 AM</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="18" customHeight="1">
       <c r="A8" s="3" t="inlineStr">
@@ -4746,11 +4732,11 @@
           <t>10:30 AM</t>
         </is>
       </c>
-      <c r="B8" s="4" t="n"/>
+      <c r="B8" s="6" t="n"/>
       <c r="C8" s="6" t="n"/>
-      <c r="D8" s="4" t="n"/>
+      <c r="D8" s="6" t="n"/>
       <c r="E8" s="6" t="n"/>
-      <c r="F8" s="4" t="n"/>
+      <c r="F8" s="6" t="n"/>
     </row>
     <row r="9" ht="18" customHeight="1">
       <c r="A9" s="3" t="inlineStr">
@@ -4854,11 +4840,29 @@
           <t>2:00 PM</t>
         </is>
       </c>
-      <c r="B15" s="4" t="n"/>
+      <c r="B15" s="9" t="inlineStr">
+        <is>
+          <t>MATH 1003-007
+Corley 101
+2:00 PM-2:50 PM</t>
+        </is>
+      </c>
       <c r="C15" s="4" t="n"/>
-      <c r="D15" s="4" t="n"/>
+      <c r="D15" s="9" t="inlineStr">
+        <is>
+          <t>MATH 1003-007
+Corley 101
+2:00 PM-2:50 PM</t>
+        </is>
+      </c>
       <c r="E15" s="6" t="n"/>
-      <c r="F15" s="4" t="n"/>
+      <c r="F15" s="9" t="inlineStr">
+        <is>
+          <t>MATH 1003-007
+Corley 101
+2:00 PM-2:50 PM</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="18" customHeight="1">
       <c r="A16" s="3" t="inlineStr">
@@ -4866,11 +4870,17 @@
           <t>2:30 PM</t>
         </is>
       </c>
-      <c r="B16" s="4" t="n"/>
-      <c r="C16" s="4" t="n"/>
-      <c r="D16" s="4" t="n"/>
+      <c r="B16" s="6" t="n"/>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>MATH 2914-001
+Corley 101
+2:30 PM-3:50 PM</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="n"/>
       <c r="E16" s="4" t="n"/>
-      <c r="F16" s="4" t="n"/>
+      <c r="F16" s="6" t="n"/>
     </row>
     <row r="17" ht="18" customHeight="1">
       <c r="A17" s="3" t="inlineStr">
@@ -4879,7 +4889,7 @@
         </is>
       </c>
       <c r="B17" s="4" t="n"/>
-      <c r="C17" s="4" t="n"/>
+      <c r="C17" s="8" t="n"/>
       <c r="D17" s="4" t="n"/>
       <c r="E17" s="4" t="n"/>
       <c r="F17" s="4" t="n"/>
@@ -4891,7 +4901,7 @@
         </is>
       </c>
       <c r="B18" s="4" t="n"/>
-      <c r="C18" s="4" t="n"/>
+      <c r="C18" s="6" t="n"/>
       <c r="D18" s="4" t="n"/>
       <c r="E18" s="4" t="n"/>
       <c r="F18" s="4" t="n"/>
@@ -4920,34 +4930,25 @@
       <c r="E20" s="4" t="n"/>
       <c r="F20" s="4" t="n"/>
     </row>
-    <row r="23">
-      <c r="A23" s="9" t="inlineStr">
-        <is>
-          <t>Online / TBA</t>
-        </is>
-      </c>
-      <c r="B23" s="10" t="inlineStr">
-        <is>
-          <t>MATH 2703-TC1</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <autoFilter ref="A2:F20"/>
-  <mergeCells count="14">
+  <mergeCells count="17">
     <mergeCell ref="E13:E15"/>
     <mergeCell ref="F13:F14"/>
+    <mergeCell ref="D15:D16"/>
+    <mergeCell ref="F15:F16"/>
     <mergeCell ref="B13:B14"/>
-    <mergeCell ref="B3:B4"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="D13:D14"/>
-    <mergeCell ref="F3:F4"/>
-    <mergeCell ref="D3:D4"/>
-    <mergeCell ref="B23:F23"/>
+    <mergeCell ref="C16:C18"/>
+    <mergeCell ref="D7:D8"/>
+    <mergeCell ref="B7:B8"/>
+    <mergeCell ref="F7:F8"/>
     <mergeCell ref="F5:F6"/>
     <mergeCell ref="C6:C8"/>
     <mergeCell ref="E6:E8"/>
     <mergeCell ref="B5:B6"/>
+    <mergeCell ref="B15:B16"/>
     <mergeCell ref="D5:D6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5041,11 +5042,29 @@
           <t>9:00 AM</t>
         </is>
       </c>
-      <c r="B5" s="4" t="n"/>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>MATH 1003-006
+Rothwell 221
+9:00 AM-9:50 AM</t>
+        </is>
+      </c>
       <c r="C5" s="4" t="n"/>
-      <c r="D5" s="4" t="n"/>
+      <c r="D5" s="7" t="inlineStr">
+        <is>
+          <t>MATH 1003-006
+Rothwell 221
+9:00 AM-9:50 AM</t>
+        </is>
+      </c>
       <c r="E5" s="4" t="n"/>
-      <c r="F5" s="4" t="n"/>
+      <c r="F5" s="7" t="inlineStr">
+        <is>
+          <t>MATH 1003-006
+Rothwell 221
+9:00 AM-9:50 AM</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="18" customHeight="1">
       <c r="A6" s="3" t="inlineStr">
@@ -5053,11 +5072,11 @@
           <t>9:30 AM</t>
         </is>
       </c>
-      <c r="B6" s="4" t="n"/>
+      <c r="B6" s="6" t="n"/>
       <c r="C6" s="4" t="n"/>
-      <c r="D6" s="4" t="n"/>
+      <c r="D6" s="6" t="n"/>
       <c r="E6" s="4" t="n"/>
-      <c r="F6" s="4" t="n"/>
+      <c r="F6" s="6" t="n"/>
     </row>
     <row r="7" ht="18" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
@@ -5065,7 +5084,7 @@
           <t>10:00 AM</t>
         </is>
       </c>
-      <c r="B7" s="7" t="inlineStr">
+      <c r="B7" s="12" t="inlineStr">
         <is>
           <t>STAT 2163-001
 Rothwell 221
@@ -5073,7 +5092,7 @@
         </is>
       </c>
       <c r="C7" s="4" t="n"/>
-      <c r="D7" s="7" t="inlineStr">
+      <c r="D7" s="12" t="inlineStr">
         <is>
           <t>STAT 2163-001
 Rothwell 221
@@ -5081,7 +5100,7 @@
         </is>
       </c>
       <c r="E7" s="4" t="n"/>
-      <c r="F7" s="7" t="inlineStr">
+      <c r="F7" s="12" t="inlineStr">
         <is>
           <t>STAT 2163-001
 Rothwell 221
@@ -5179,29 +5198,11 @@
           <t>2:00 PM</t>
         </is>
       </c>
-      <c r="B15" s="13" t="inlineStr">
-        <is>
-          <t>STAT 2163-004
-Corley 268
-2:00 PM-2:50 PM</t>
-        </is>
-      </c>
+      <c r="B15" s="4" t="n"/>
       <c r="C15" s="4" t="n"/>
-      <c r="D15" s="13" t="inlineStr">
-        <is>
-          <t>STAT 2163-004
-Corley 268
-2:00 PM-2:50 PM</t>
-        </is>
-      </c>
+      <c r="D15" s="4" t="n"/>
       <c r="E15" s="4" t="n"/>
-      <c r="F15" s="13" t="inlineStr">
-        <is>
-          <t>STAT 2163-004
-Corley 268
-2:00 PM-2:50 PM</t>
-        </is>
-      </c>
+      <c r="F15" s="4" t="n"/>
     </row>
     <row r="16" ht="18" customHeight="1">
       <c r="A16" s="3" t="inlineStr">
@@ -5209,11 +5210,11 @@
           <t>2:30 PM</t>
         </is>
       </c>
-      <c r="B16" s="6" t="n"/>
+      <c r="B16" s="4" t="n"/>
       <c r="C16" s="4" t="n"/>
-      <c r="D16" s="6" t="n"/>
+      <c r="D16" s="4" t="n"/>
       <c r="E16" s="4" t="n"/>
-      <c r="F16" s="6" t="n"/>
+      <c r="F16" s="4" t="n"/>
     </row>
     <row r="17" ht="18" customHeight="1">
       <c r="A17" s="3" t="inlineStr">
@@ -5264,12 +5265,12 @@
       <c r="F20" s="4" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="9" t="inlineStr">
+      <c r="A23" s="10" t="inlineStr">
         <is>
           <t>Online / TBA</t>
         </is>
       </c>
-      <c r="B23" s="10" t="inlineStr">
+      <c r="B23" s="11" t="inlineStr">
         <is>
           <t>MATH 0803-TC1, MATH 1003-TC1, MATH 1003-TC2</t>
         </is>
@@ -5278,14 +5279,14 @@
   </sheetData>
   <autoFilter ref="A2:F20"/>
   <mergeCells count="8">
-    <mergeCell ref="F15:F16"/>
-    <mergeCell ref="D15:D16"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="D7:D8"/>
     <mergeCell ref="B7:B8"/>
     <mergeCell ref="B23:F23"/>
     <mergeCell ref="F7:F8"/>
-    <mergeCell ref="B15:B16"/>
+    <mergeCell ref="F5:F6"/>
+    <mergeCell ref="B5:B6"/>
+    <mergeCell ref="D5:D6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>
@@ -5293,6 +5294,389 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:F20"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="23" customWidth="1" min="2" max="2"/>
+    <col width="23" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="4" max="4"/>
+    <col width="23" customWidth="1" min="5" max="5"/>
+    <col width="23" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Instructor Schedule -- Limperis, Thomas G.</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Time</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Monday</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="18" customHeight="1">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>8:00 AM</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="n"/>
+      <c r="C3" s="4" t="n"/>
+      <c r="D3" s="4" t="n"/>
+      <c r="E3" s="4" t="n"/>
+      <c r="F3" s="4" t="n"/>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>8:30 AM</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="n"/>
+      <c r="C4" s="4" t="n"/>
+      <c r="D4" s="4" t="n"/>
+      <c r="E4" s="4" t="n"/>
+      <c r="F4" s="4" t="n"/>
+    </row>
+    <row r="5" ht="18" customHeight="1">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>9:00 AM</t>
+        </is>
+      </c>
+      <c r="B5" s="12" t="inlineStr">
+        <is>
+          <t>MATH 3243-002
+Rothwell 212
+9:00 AM-9:50 AM</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="n"/>
+      <c r="D5" s="12" t="inlineStr">
+        <is>
+          <t>MATH 3243-002
+Rothwell 212
+9:00 AM-9:50 AM</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="n"/>
+      <c r="F5" s="12" t="inlineStr">
+        <is>
+          <t>MATH 3243-002
+Rothwell 212
+9:00 AM-9:50 AM</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="18" customHeight="1">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>9:30 AM</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="n"/>
+      <c r="C6" s="4" t="n"/>
+      <c r="D6" s="6" t="n"/>
+      <c r="E6" s="4" t="n"/>
+      <c r="F6" s="6" t="n"/>
+    </row>
+    <row r="7" ht="18" customHeight="1">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>10:00 AM</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="n"/>
+      <c r="C7" s="4" t="n"/>
+      <c r="D7" s="4" t="n"/>
+      <c r="E7" s="4" t="n"/>
+      <c r="F7" s="4" t="n"/>
+    </row>
+    <row r="8" ht="18" customHeight="1">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>10:30 AM</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="n"/>
+      <c r="C8" s="4" t="n"/>
+      <c r="D8" s="4" t="n"/>
+      <c r="E8" s="4" t="n"/>
+      <c r="F8" s="4" t="n"/>
+    </row>
+    <row r="9" ht="18" customHeight="1">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>11:00 AM</t>
+        </is>
+      </c>
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>MATH 2934-002
+Corley 103
+11:00 AM-11:50 AM</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="n"/>
+      <c r="D9" s="7" t="inlineStr">
+        <is>
+          <t>MATH 2934-002
+Corley 103
+11:00 AM-11:50 AM</t>
+        </is>
+      </c>
+      <c r="E9" s="7" t="inlineStr">
+        <is>
+          <t>MATH 2934-002
+Corley 101
+11:00 AM-12:20 PM</t>
+        </is>
+      </c>
+      <c r="F9" s="7" t="inlineStr">
+        <is>
+          <t>MATH 2934-002
+Corley 103
+11:00 AM-11:50 AM</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="18" customHeight="1">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>11:30 AM</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="n"/>
+      <c r="C10" s="4" t="n"/>
+      <c r="D10" s="6" t="n"/>
+      <c r="E10" s="8" t="n"/>
+      <c r="F10" s="6" t="n"/>
+    </row>
+    <row r="11" ht="18" customHeight="1">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>12:00 PM</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="n"/>
+      <c r="C11" s="4" t="n"/>
+      <c r="D11" s="4" t="n"/>
+      <c r="E11" s="6" t="n"/>
+      <c r="F11" s="4" t="n"/>
+    </row>
+    <row r="12" ht="18" customHeight="1">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>12:30 PM</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="n"/>
+      <c r="C12" s="4" t="n"/>
+      <c r="D12" s="4" t="n"/>
+      <c r="E12" s="4" t="n"/>
+      <c r="F12" s="4" t="n"/>
+    </row>
+    <row r="13" ht="18" customHeight="1">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>1:00 PM</t>
+        </is>
+      </c>
+      <c r="B13" s="13" t="inlineStr">
+        <is>
+          <t>MATH 4123-001
+Corley 268
+1:00 PM-1:50 PM
+/ MATH 4123-H01</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="n"/>
+      <c r="D13" s="13" t="inlineStr">
+        <is>
+          <t>MATH 4123-001
+Corley 268
+1:00 PM-1:50 PM
+/ MATH 4123-H01</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="n"/>
+      <c r="F13" s="13" t="inlineStr">
+        <is>
+          <t>MATH 4123-001
+Corley 268
+1:00 PM-1:50 PM
+/ MATH 4123-H01</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="18" customHeight="1">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>1:30 PM</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="n"/>
+      <c r="C14" s="4" t="n"/>
+      <c r="D14" s="6" t="n"/>
+      <c r="E14" s="4" t="n"/>
+      <c r="F14" s="6" t="n"/>
+    </row>
+    <row r="15" ht="18" customHeight="1">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>2:00 PM</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>MATH 2914-003
+Corley 268
+2:00 PM-2:50 PM</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="n"/>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>MATH 2914-003
+Corley 268
+2:00 PM-2:50 PM</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="n"/>
+      <c r="F15" s="5" t="inlineStr">
+        <is>
+          <t>MATH 2914-003
+Corley 268
+2:00 PM-2:50 PM</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="18" customHeight="1">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>2:30 PM</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="n"/>
+      <c r="C16" s="4" t="n"/>
+      <c r="D16" s="6" t="n"/>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>MATH 2914-003
+Corley 101
+2:30 PM-3:50 PM</t>
+        </is>
+      </c>
+      <c r="F16" s="6" t="n"/>
+    </row>
+    <row r="17" ht="18" customHeight="1">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>3:00 PM</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="n"/>
+      <c r="C17" s="4" t="n"/>
+      <c r="D17" s="4" t="n"/>
+      <c r="E17" s="8" t="n"/>
+      <c r="F17" s="4" t="n"/>
+    </row>
+    <row r="18" ht="18" customHeight="1">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>3:30 PM</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="n"/>
+      <c r="C18" s="4" t="n"/>
+      <c r="D18" s="4" t="n"/>
+      <c r="E18" s="6" t="n"/>
+      <c r="F18" s="4" t="n"/>
+    </row>
+    <row r="19" ht="18" customHeight="1">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>4:00 PM</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="n"/>
+      <c r="C19" s="4" t="n"/>
+      <c r="D19" s="4" t="n"/>
+      <c r="E19" s="4" t="n"/>
+      <c r="F19" s="4" t="n"/>
+    </row>
+    <row r="20" ht="18" customHeight="1">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>4:30 PM</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="n"/>
+      <c r="C20" s="4" t="n"/>
+      <c r="D20" s="4" t="n"/>
+      <c r="E20" s="4" t="n"/>
+      <c r="F20" s="4" t="n"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A2:F20"/>
+  <mergeCells count="15">
+    <mergeCell ref="F15:F16"/>
+    <mergeCell ref="F13:F14"/>
+    <mergeCell ref="B9:B10"/>
+    <mergeCell ref="E9:E11"/>
+    <mergeCell ref="D9:D10"/>
+    <mergeCell ref="D15:D16"/>
+    <mergeCell ref="F9:F10"/>
+    <mergeCell ref="B13:B14"/>
+    <mergeCell ref="E16:E18"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="D13:D14"/>
+    <mergeCell ref="F5:F6"/>
+    <mergeCell ref="B5:B6"/>
+    <mergeCell ref="B15:B16"/>
+    <mergeCell ref="D5:D6"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup fitToHeight="0" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5312,7 +5696,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Instructor Schedule -- Limperis, Thomas G.</t>
+          <t>Instructor Schedule -- Overduin, Matthew D.</t>
         </is>
       </c>
     </row>
@@ -5391,12 +5775,18 @@
         </is>
       </c>
       <c r="B6" s="4" t="n"/>
-      <c r="C6" s="4" t="n"/>
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>MATH 2243-002
+Ross Pendergraft Library 220
+9:30 AM-10:50 AM</t>
+        </is>
+      </c>
       <c r="D6" s="4" t="n"/>
-      <c r="E6" s="5" t="inlineStr">
-        <is>
-          <t>MATH 2924-003
-Rothwell 206
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>MATH 2243-002
+Ross Pendergraft Library 220
 9:30 AM-10:50 AM</t>
         </is>
       </c>
@@ -5408,29 +5798,11 @@
           <t>10:00 AM</t>
         </is>
       </c>
-      <c r="B7" s="5" t="inlineStr">
-        <is>
-          <t>MATH 2924-003
-Rothwell 306
-10:00 AM-10:50 AM</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="n"/>
-      <c r="D7" s="5" t="inlineStr">
-        <is>
-          <t>MATH 2924-003
-Rothwell 306
-10:00 AM-10:50 AM</t>
-        </is>
-      </c>
+      <c r="B7" s="4" t="n"/>
+      <c r="C7" s="8" t="n"/>
+      <c r="D7" s="4" t="n"/>
       <c r="E7" s="8" t="n"/>
-      <c r="F7" s="5" t="inlineStr">
-        <is>
-          <t>MATH 2924-003
-Rothwell 306
-10:00 AM-10:50 AM</t>
-        </is>
-      </c>
+      <c r="F7" s="4" t="n"/>
     </row>
     <row r="8" ht="18" customHeight="1">
       <c r="A8" s="3" t="inlineStr">
@@ -5438,11 +5810,11 @@
           <t>10:30 AM</t>
         </is>
       </c>
-      <c r="B8" s="6" t="n"/>
-      <c r="C8" s="4" t="n"/>
-      <c r="D8" s="6" t="n"/>
+      <c r="B8" s="4" t="n"/>
+      <c r="C8" s="6" t="n"/>
+      <c r="D8" s="4" t="n"/>
       <c r="E8" s="6" t="n"/>
-      <c r="F8" s="6" t="n"/>
+      <c r="F8" s="4" t="n"/>
     </row>
     <row r="9" ht="18" customHeight="1">
       <c r="A9" s="3" t="inlineStr">
@@ -5451,21 +5823,9 @@
         </is>
       </c>
       <c r="B9" s="4" t="n"/>
-      <c r="C9" s="7" t="inlineStr">
-        <is>
-          <t>MATH 2703-002
-Rothwell 206
-11:00 AM-12:20 PM</t>
-        </is>
-      </c>
+      <c r="C9" s="4" t="n"/>
       <c r="D9" s="4" t="n"/>
-      <c r="E9" s="7" t="inlineStr">
-        <is>
-          <t>MATH 2703-002
-Rothwell 206
-11:00 AM-12:20 PM</t>
-        </is>
-      </c>
+      <c r="E9" s="4" t="n"/>
       <c r="F9" s="4" t="n"/>
     </row>
     <row r="10" ht="18" customHeight="1">
@@ -5475,9 +5835,9 @@
         </is>
       </c>
       <c r="B10" s="4" t="n"/>
-      <c r="C10" s="8" t="n"/>
+      <c r="C10" s="4" t="n"/>
       <c r="D10" s="4" t="n"/>
-      <c r="E10" s="8" t="n"/>
+      <c r="E10" s="4" t="n"/>
       <c r="F10" s="4" t="n"/>
     </row>
     <row r="11" ht="18" customHeight="1">
@@ -5486,29 +5846,11 @@
           <t>12:00 PM</t>
         </is>
       </c>
-      <c r="B11" s="11" t="inlineStr">
-        <is>
-          <t>MATH 2924-002
-Rothwell 206
-12:00 PM-12:50 PM</t>
-        </is>
-      </c>
-      <c r="C11" s="6" t="n"/>
-      <c r="D11" s="11" t="inlineStr">
-        <is>
-          <t>MATH 2924-002
-Rothwell 206
-12:00 PM-12:50 PM</t>
-        </is>
-      </c>
-      <c r="E11" s="6" t="n"/>
-      <c r="F11" s="11" t="inlineStr">
-        <is>
-          <t>MATH 2924-002
-Rothwell 206
-12:00 PM-12:50 PM</t>
-        </is>
-      </c>
+      <c r="B11" s="4" t="n"/>
+      <c r="C11" s="4" t="n"/>
+      <c r="D11" s="4" t="n"/>
+      <c r="E11" s="4" t="n"/>
+      <c r="F11" s="4" t="n"/>
     </row>
     <row r="12" ht="18" customHeight="1">
       <c r="A12" s="3" t="inlineStr">
@@ -5516,11 +5858,11 @@
           <t>12:30 PM</t>
         </is>
       </c>
-      <c r="B12" s="6" t="n"/>
+      <c r="B12" s="4" t="n"/>
       <c r="C12" s="4" t="n"/>
-      <c r="D12" s="6" t="n"/>
+      <c r="D12" s="4" t="n"/>
       <c r="E12" s="4" t="n"/>
-      <c r="F12" s="6" t="n"/>
+      <c r="F12" s="4" t="n"/>
     </row>
     <row r="13" ht="18" customHeight="1">
       <c r="A13" s="3" t="inlineStr">
@@ -5528,17 +5870,29 @@
           <t>1:00 PM</t>
         </is>
       </c>
-      <c r="B13" s="4" t="n"/>
-      <c r="C13" s="11" t="inlineStr">
-        <is>
-          <t>MATH 2924-002
-Rothwell 206
-1:00 PM-2:20 PM</t>
-        </is>
-      </c>
-      <c r="D13" s="4" t="n"/>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>MATH 2243-001
+Corley 104
+1:00 PM-1:50 PM</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="n"/>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>MATH 2243-001
+Corley 104
+1:00 PM-1:50 PM</t>
+        </is>
+      </c>
       <c r="E13" s="4" t="n"/>
-      <c r="F13" s="4" t="n"/>
+      <c r="F13" s="5" t="inlineStr">
+        <is>
+          <t>MATH 2243-001
+Corley 104
+1:00 PM-1:50 PM</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="18" customHeight="1">
       <c r="A14" s="3" t="inlineStr">
@@ -5546,11 +5900,11 @@
           <t>1:30 PM</t>
         </is>
       </c>
-      <c r="B14" s="4" t="n"/>
-      <c r="C14" s="8" t="n"/>
-      <c r="D14" s="4" t="n"/>
+      <c r="B14" s="6" t="n"/>
+      <c r="C14" s="4" t="n"/>
+      <c r="D14" s="6" t="n"/>
       <c r="E14" s="4" t="n"/>
-      <c r="F14" s="4" t="n"/>
+      <c r="F14" s="6" t="n"/>
     </row>
     <row r="15" ht="18" customHeight="1">
       <c r="A15" s="3" t="inlineStr">
@@ -5558,11 +5912,29 @@
           <t>2:00 PM</t>
         </is>
       </c>
-      <c r="B15" s="4" t="n"/>
-      <c r="C15" s="6" t="n"/>
-      <c r="D15" s="4" t="n"/>
+      <c r="B15" s="12" t="inlineStr">
+        <is>
+          <t>MATH 3123-001
+Corley 102
+2:00 PM-2:50 PM</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="n"/>
+      <c r="D15" s="12" t="inlineStr">
+        <is>
+          <t>MATH 3123-001
+Corley 102
+2:00 PM-2:50 PM</t>
+        </is>
+      </c>
       <c r="E15" s="4" t="n"/>
-      <c r="F15" s="4" t="n"/>
+      <c r="F15" s="12" t="inlineStr">
+        <is>
+          <t>MATH 3123-001
+Corley 102
+2:00 PM-2:50 PM</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="18" customHeight="1">
       <c r="A16" s="3" t="inlineStr">
@@ -5570,11 +5942,11 @@
           <t>2:30 PM</t>
         </is>
       </c>
-      <c r="B16" s="4" t="n"/>
+      <c r="B16" s="6" t="n"/>
       <c r="C16" s="4" t="n"/>
-      <c r="D16" s="4" t="n"/>
+      <c r="D16" s="6" t="n"/>
       <c r="E16" s="4" t="n"/>
-      <c r="F16" s="4" t="n"/>
+      <c r="F16" s="6" t="n"/>
     </row>
     <row r="17" ht="18" customHeight="1">
       <c r="A17" s="3" t="inlineStr">
@@ -5625,391 +5997,27 @@
       <c r="F20" s="4" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="9" t="inlineStr">
+      <c r="A23" s="10" t="inlineStr">
         <is>
           <t>Online / TBA</t>
         </is>
       </c>
-      <c r="B23" s="10" t="inlineStr">
-        <is>
-          <t>MATH 4993-001</t>
+      <c r="B23" s="11" t="inlineStr">
+        <is>
+          <t>MATH 2703-TC1</t>
         </is>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A2:F20"/>
-  <mergeCells count="12">
-    <mergeCell ref="C13:C15"/>
-    <mergeCell ref="E9:E11"/>
+  <mergeCells count="10">
+    <mergeCell ref="F15:F16"/>
+    <mergeCell ref="F13:F14"/>
+    <mergeCell ref="D15:D16"/>
+    <mergeCell ref="B13:B14"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="D7:D8"/>
-    <mergeCell ref="B7:B8"/>
-    <mergeCell ref="B11:B12"/>
+    <mergeCell ref="D13:D14"/>
     <mergeCell ref="B23:F23"/>
-    <mergeCell ref="D11:D12"/>
-    <mergeCell ref="F7:F8"/>
-    <mergeCell ref="F11:F12"/>
-    <mergeCell ref="C9:C11"/>
-    <mergeCell ref="E6:E8"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup fitToHeight="0" fitToWidth="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:F20"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="23" customWidth="1" min="2" max="2"/>
-    <col width="23" customWidth="1" min="3" max="3"/>
-    <col width="23" customWidth="1" min="4" max="4"/>
-    <col width="23" customWidth="1" min="5" max="5"/>
-    <col width="23" customWidth="1" min="6" max="6"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Instructor Schedule -- Overduin, Matthew D.</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Time</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>Monday</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>Tuesday</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>Wednesday</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>Thursday</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>Friday</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="18" customHeight="1">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>8:00 AM</t>
-        </is>
-      </c>
-      <c r="B3" s="11" t="inlineStr">
-        <is>
-          <t>MATH 3203-001
-Corley 268
-8:00 AM-8:50 AM
-/ MATH 3203-H01</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="n"/>
-      <c r="D3" s="11" t="inlineStr">
-        <is>
-          <t>MATH 3203-001
-Corley 268
-8:00 AM-8:50 AM
-/ MATH 3203-H01</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="n"/>
-      <c r="F3" s="11" t="inlineStr">
-        <is>
-          <t>MATH 3203-001
-Corley 268
-8:00 AM-8:50 AM
-/ MATH 3203-H01</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="18" customHeight="1">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>8:30 AM</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="n"/>
-      <c r="C4" s="4" t="n"/>
-      <c r="D4" s="6" t="n"/>
-      <c r="E4" s="4" t="n"/>
-      <c r="F4" s="6" t="n"/>
-    </row>
-    <row r="5" ht="18" customHeight="1">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>9:00 AM</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="n"/>
-      <c r="C5" s="4" t="n"/>
-      <c r="D5" s="4" t="n"/>
-      <c r="E5" s="4" t="n"/>
-      <c r="F5" s="4" t="n"/>
-    </row>
-    <row r="6" ht="18" customHeight="1">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>9:30 AM</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="n"/>
-      <c r="C6" s="5" t="inlineStr">
-        <is>
-          <t>MATH 2243-002
-Ross Pendergraft Library 220
-9:30 AM-10:50 AM</t>
-        </is>
-      </c>
-      <c r="D6" s="4" t="n"/>
-      <c r="E6" s="5" t="inlineStr">
-        <is>
-          <t>MATH 2243-002
-Ross Pendergraft Library 220
-9:30 AM-10:50 AM</t>
-        </is>
-      </c>
-      <c r="F6" s="4" t="n"/>
-    </row>
-    <row r="7" ht="18" customHeight="1">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>10:00 AM</t>
-        </is>
-      </c>
-      <c r="B7" s="7" t="inlineStr">
-        <is>
-          <t>MATH 2703-001
-Corley 101
-10:00 AM-10:50 AM</t>
-        </is>
-      </c>
-      <c r="C7" s="8" t="n"/>
-      <c r="D7" s="7" t="inlineStr">
-        <is>
-          <t>MATH 2703-001
-Corley 101
-10:00 AM-10:50 AM</t>
-        </is>
-      </c>
-      <c r="E7" s="8" t="n"/>
-      <c r="F7" s="7" t="inlineStr">
-        <is>
-          <t>MATH 2703-001
-Corley 101
-10:00 AM-10:50 AM</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="18" customHeight="1">
-      <c r="A8" s="3" t="inlineStr">
-        <is>
-          <t>10:30 AM</t>
-        </is>
-      </c>
-      <c r="B8" s="6" t="n"/>
-      <c r="C8" s="6" t="n"/>
-      <c r="D8" s="6" t="n"/>
-      <c r="E8" s="6" t="n"/>
-      <c r="F8" s="6" t="n"/>
-    </row>
-    <row r="9" ht="18" customHeight="1">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t>11:00 AM</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="n"/>
-      <c r="C9" s="4" t="n"/>
-      <c r="D9" s="4" t="n"/>
-      <c r="E9" s="4" t="n"/>
-      <c r="F9" s="4" t="n"/>
-    </row>
-    <row r="10" ht="18" customHeight="1">
-      <c r="A10" s="3" t="inlineStr">
-        <is>
-          <t>11:30 AM</t>
-        </is>
-      </c>
-      <c r="B10" s="4" t="n"/>
-      <c r="C10" s="4" t="n"/>
-      <c r="D10" s="4" t="n"/>
-      <c r="E10" s="4" t="n"/>
-      <c r="F10" s="4" t="n"/>
-    </row>
-    <row r="11" ht="18" customHeight="1">
-      <c r="A11" s="3" t="inlineStr">
-        <is>
-          <t>12:00 PM</t>
-        </is>
-      </c>
-      <c r="B11" s="4" t="n"/>
-      <c r="C11" s="4" t="n"/>
-      <c r="D11" s="4" t="n"/>
-      <c r="E11" s="4" t="n"/>
-      <c r="F11" s="4" t="n"/>
-    </row>
-    <row r="12" ht="18" customHeight="1">
-      <c r="A12" s="3" t="inlineStr">
-        <is>
-          <t>12:30 PM</t>
-        </is>
-      </c>
-      <c r="B12" s="4" t="n"/>
-      <c r="C12" s="4" t="n"/>
-      <c r="D12" s="4" t="n"/>
-      <c r="E12" s="4" t="n"/>
-      <c r="F12" s="4" t="n"/>
-    </row>
-    <row r="13" ht="18" customHeight="1">
-      <c r="A13" s="3" t="inlineStr">
-        <is>
-          <t>1:00 PM</t>
-        </is>
-      </c>
-      <c r="B13" s="4" t="n"/>
-      <c r="C13" s="4" t="n"/>
-      <c r="D13" s="4" t="n"/>
-      <c r="E13" s="4" t="n"/>
-      <c r="F13" s="4" t="n"/>
-    </row>
-    <row r="14" ht="18" customHeight="1">
-      <c r="A14" s="3" t="inlineStr">
-        <is>
-          <t>1:30 PM</t>
-        </is>
-      </c>
-      <c r="B14" s="4" t="n"/>
-      <c r="C14" s="4" t="n"/>
-      <c r="D14" s="4" t="n"/>
-      <c r="E14" s="4" t="n"/>
-      <c r="F14" s="4" t="n"/>
-    </row>
-    <row r="15" ht="18" customHeight="1">
-      <c r="A15" s="3" t="inlineStr">
-        <is>
-          <t>2:00 PM</t>
-        </is>
-      </c>
-      <c r="B15" s="13" t="inlineStr">
-        <is>
-          <t>MATH 3123-001
-Corley 102
-2:00 PM-2:50 PM</t>
-        </is>
-      </c>
-      <c r="C15" s="4" t="n"/>
-      <c r="D15" s="13" t="inlineStr">
-        <is>
-          <t>MATH 3123-001
-Corley 102
-2:00 PM-2:50 PM</t>
-        </is>
-      </c>
-      <c r="E15" s="4" t="n"/>
-      <c r="F15" s="13" t="inlineStr">
-        <is>
-          <t>MATH 3123-001
-Corley 102
-2:00 PM-2:50 PM</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="18" customHeight="1">
-      <c r="A16" s="3" t="inlineStr">
-        <is>
-          <t>2:30 PM</t>
-        </is>
-      </c>
-      <c r="B16" s="6" t="n"/>
-      <c r="C16" s="4" t="n"/>
-      <c r="D16" s="6" t="n"/>
-      <c r="E16" s="4" t="n"/>
-      <c r="F16" s="6" t="n"/>
-    </row>
-    <row r="17" ht="18" customHeight="1">
-      <c r="A17" s="3" t="inlineStr">
-        <is>
-          <t>3:00 PM</t>
-        </is>
-      </c>
-      <c r="B17" s="4" t="n"/>
-      <c r="C17" s="4" t="n"/>
-      <c r="D17" s="4" t="n"/>
-      <c r="E17" s="4" t="n"/>
-      <c r="F17" s="4" t="n"/>
-    </row>
-    <row r="18" ht="18" customHeight="1">
-      <c r="A18" s="3" t="inlineStr">
-        <is>
-          <t>3:30 PM</t>
-        </is>
-      </c>
-      <c r="B18" s="4" t="n"/>
-      <c r="C18" s="4" t="n"/>
-      <c r="D18" s="4" t="n"/>
-      <c r="E18" s="4" t="n"/>
-      <c r="F18" s="4" t="n"/>
-    </row>
-    <row r="19" ht="18" customHeight="1">
-      <c r="A19" s="3" t="inlineStr">
-        <is>
-          <t>4:00 PM</t>
-        </is>
-      </c>
-      <c r="B19" s="4" t="n"/>
-      <c r="C19" s="4" t="n"/>
-      <c r="D19" s="4" t="n"/>
-      <c r="E19" s="4" t="n"/>
-      <c r="F19" s="4" t="n"/>
-    </row>
-    <row r="20" ht="18" customHeight="1">
-      <c r="A20" s="3" t="inlineStr">
-        <is>
-          <t>4:30 PM</t>
-        </is>
-      </c>
-      <c r="B20" s="4" t="n"/>
-      <c r="C20" s="4" t="n"/>
-      <c r="D20" s="4" t="n"/>
-      <c r="E20" s="4" t="n"/>
-      <c r="F20" s="4" t="n"/>
-    </row>
-  </sheetData>
-  <autoFilter ref="A2:F20"/>
-  <mergeCells count="12">
-    <mergeCell ref="F15:F16"/>
-    <mergeCell ref="D15:D16"/>
-    <mergeCell ref="B3:B4"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="D7:D8"/>
-    <mergeCell ref="F3:F4"/>
-    <mergeCell ref="D3:D4"/>
-    <mergeCell ref="B7:B8"/>
-    <mergeCell ref="F7:F8"/>
     <mergeCell ref="C6:C8"/>
     <mergeCell ref="B15:B16"/>
     <mergeCell ref="E6:E8"/>
